--- a/artfynd/A 17781-2024 artfynd.xlsx
+++ b/artfynd/A 17781-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla  Henriksson, Christer Pålsson</t>
+          <t>Christer Pålsson, Ulla  Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 17781-2024 artfynd.xlsx
+++ b/artfynd/A 17781-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118400673</v>
+        <v>118400585</v>
       </c>
       <c r="B2" t="n">
-        <v>97848</v>
+        <v>106389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219811</v>
+        <v>220015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -761,6 +769,11 @@
           <t>2024-07-11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst 200 stjälkar i begynnande blomning. Alla till synes vitblommiga.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,7 +786,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -791,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118400585</v>
+        <v>118400673</v>
       </c>
       <c r="B3" t="n">
-        <v>106382</v>
+        <v>97855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,33 +820,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220015</v>
+        <v>219811</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -885,11 +890,6 @@
           <t>2024-07-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst 200 stjälkar i begynnande blomning. Alla till synes vitblommiga.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +902,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 17781-2024 artfynd.xlsx
+++ b/artfynd/A 17781-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118400585</v>
+        <v>118400673</v>
       </c>
       <c r="B2" t="n">
-        <v>106389</v>
+        <v>97855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220015</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -769,11 +761,6 @@
           <t>2024-07-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst 200 stjälkar i begynnande blomning. Alla till synes vitblommiga.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -786,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,17 +784,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Pålsson, Ulla  Henriksson</t>
+          <t>Ulla  Henriksson, Christer Pålsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118400673</v>
+        <v>118400585</v>
       </c>
       <c r="B3" t="n">
-        <v>97855</v>
+        <v>106389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,25 +807,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>220015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -890,6 +885,11 @@
           <t>2024-07-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 200 stjälkar i begynnande blomning. Alla till synes vitblommiga.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +902,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
